--- a/data/trans_orig/IP07KS_C09_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C09_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de ir bien en el colegio en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de ir bien en el colegio, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8135</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4182</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11812</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,95%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5217</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2536</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8591</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>42,05%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>10042</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17735</t>
+          <t>19719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>64,2%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3339</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7600</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>19,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6219</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3152</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9103</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>50,13%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>73,37%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>10338</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15107</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,46%</t>
         </is>
       </c>
     </row>
@@ -946,107 +946,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5472</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12,59%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>32,64%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2195</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5331</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>31,82%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>550</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>954</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8743</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>907</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -1172,107 +1172,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3425</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2776</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>20,45%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3156</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>103298</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>87908</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>120949</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51,73%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,58%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>66606</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>40824</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>85299</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41,81%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>104534</t>
+          <t>71137</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87472</t>
+          <t>60081</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122112</t>
+          <t>82545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>171140</t>
+          <t>174435</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133087</t>
+          <t>155637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196399</t>
+          <t>194634</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>56,85%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>65024</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>52234</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78708</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,16%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>50749</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>27303</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>65509</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>31,85%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17,14%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>41,12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64715</t>
+          <t>53120</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50785</t>
+          <t>43508</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78825</t>
+          <t>64019</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>115464</t>
+          <t>118144</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89795</t>
+          <t>101575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136350</t>
+          <t>135272</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26898</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16170</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43902</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>21,99%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>39325</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13284</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>87982</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>24,68%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>55,23%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28109</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17088</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46867</t>
+          <t>26987</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>67434</t>
+          <t>42526</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38480</t>
+          <t>30358</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133371</t>
+          <t>59388</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4448</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1616</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1057</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3797</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4146</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4592</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1698</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9694</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -1854,107 +1854,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1576</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1594</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6267</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7983</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1594</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6721</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1576</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6066</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>199668</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>199668</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>199668</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>201950</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>201950</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>201950</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>361263</t>
+          <t>342337</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>361263</t>
+          <t>342337</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>361263</t>
+          <t>342337</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28255</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21489</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>34480</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>53,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>40,54%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>65,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>19191</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14143</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24842</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>49,52%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,5%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>64,1%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>28243</t>
+          <t>20517</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>15260</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34390</t>
+          <t>25760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>47434</t>
+          <t>48772</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>40055</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56284</t>
+          <t>56733</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22531</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16272</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29291</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>30,7%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>18773</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13303</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24038</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>48,44%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,33%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>62,03%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22137</t>
+          <t>19592</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28502</t>
+          <t>24822</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>40910</t>
+          <t>42124</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>33718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49422</t>
+          <t>50326</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,55%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2218</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6179</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3956</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4140</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5654</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>880</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>139688</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>122386</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>159358</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>51,84%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>59,15%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>91014</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>60109</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>109311</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>43,24%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>28,56%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>51,94%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>140331</t>
+          <t>97705</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>122068</t>
+          <t>85497</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>161101</t>
+          <t>110001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>231345</t>
+          <t>237394</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>188453</t>
+          <t>214525</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>257901</t>
+          <t>261113</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>55,91%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>90894</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>75412</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>104945</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>33,73%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>27,99%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>38,95%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>75741</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>47941</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>93094</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>44,23%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>90412</t>
+          <t>79657</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>73725</t>
+          <t>67657</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>106617</t>
+          <t>91663</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>166154</t>
+          <t>170551</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>135002</t>
+          <t>148413</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>188261</t>
+          <t>190130</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>31227</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>20595</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>48641</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>18,05%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>40113</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>12588</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>101484</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>19,06%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>48,22%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>32617</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51506</t>
+          <t>26351</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>72730</t>
+          <t>47714</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44375</t>
+          <t>33956</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>153500</t>
+          <t>69302</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3128</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>14823</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>5230</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17657</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2964</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1576</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1594</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>7707</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>7114</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,27 +3293,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>269435</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>269435</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>269435</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>271397</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>271397</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>271397</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>481869</t>
+          <t>467024</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>481869</t>
+          <t>467024</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>481869</t>
+          <t>467024</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
